--- a/data/trans_orig/P32D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023</t>
+          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65611</t>
+          <t>65701</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96812</t>
+          <t>97421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56449</t>
+          <t>55852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78617</t>
+          <t>77943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>128636</t>
+          <t>129204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>169006</t>
+          <t>168441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>91069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125465</t>
+          <t>126014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42599</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62835</t>
+          <t>62727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142866</t>
+          <t>144136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181733</t>
+          <t>181565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64014</t>
+          <t>62284</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22934</t>
+          <t>23556</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41489</t>
+          <t>41202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64837</t>
+          <t>64073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97255</t>
+          <t>97353</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>15903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>40583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>46272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19477</t>
+          <t>19833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10792</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1408,97 +1408,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1521,97 +1521,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,62 +1669,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6074</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5871</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>35736</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62901</t>
+          <t>61492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68027</t>
+          <t>67935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91554</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125938</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79538</t>
+          <t>78255</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108776</t>
+          <t>107781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35057</t>
+          <t>34830</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51945</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120811</t>
+          <t>120881</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>153785</t>
+          <t>152572</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31975</t>
+          <t>31385</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56994</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>45507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71838</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>22088</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31182</t>
+          <t>31704</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1588</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,47 +2366,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>8,51%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>16746</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>8958</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>4234</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>16293</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>13628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -2542,97 +2542,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1534</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2655,97 +2655,97 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>1534</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41170</t>
+          <t>41252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9683</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>19369</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34443</t>
+          <t>33775</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55939</t>
+          <t>56632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72219</t>
+          <t>72503</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98938</t>
+          <t>101458</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>82618</t>
+          <t>83651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>112695</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69351</t>
+          <t>69565</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52899</t>
+          <t>50490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79486</t>
+          <t>78607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>24660</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>898</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,62 +3824,62 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1118</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>5121</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4374</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>80965</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>122718</t>
+          <t>122096</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>155785</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>373354</t>
+          <t>374591</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>224893</t>
+          <t>227413</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>659389</t>
+          <t>648670</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>203312</t>
+          <t>202311</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>251167</t>
+          <t>252090</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>149950</t>
+          <t>150020</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>144024</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>398464</t>
+          <t>394502</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>84539</t>
+          <t>82373</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>122738</t>
+          <t>121926</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>74780</t>
+          <t>72954</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>67363</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>180658</t>
+          <t>180817</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27549</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>71979</t>
+          <t>70486</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>26352</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>25626</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>82072</t>
+          <t>85754</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>33289</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>14351</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>28874</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>442</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4845,62 +4845,62 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>5342</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>5081</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,12 +4958,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>34104</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>45843</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>65050</t>
+          <t>63667</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>85966</t>
+          <t>85733</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>121612</t>
+          <t>121251</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>69198</t>
+          <t>69297</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>98896</t>
+          <t>99349</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>51972</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>110062</t>
+          <t>109418</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>144475</t>
+          <t>144430</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>35870</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>62285</t>
+          <t>62469</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>29134</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>54933</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>85898</t>
+          <t>85769</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>24254</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6235</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>27871</t>
+          <t>28065</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11772</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>31513</t>
+          <t>30720</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>18723</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>22388</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>447</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6092,62 +6092,62 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>10343</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>9554</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>44716</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>68419</t>
+          <t>68455</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>63957</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>105703</t>
+          <t>105160</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>38932</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>43282</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>42411</t>
+          <t>42964</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>75936</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -6626,12 +6626,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>14907</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>46083</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>29622</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>64382</t>
+          <t>66328</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>22114</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>23387</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>12514</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -7078,97 +7078,97 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>2082</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>4593</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>6736</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>2082</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="S60" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>7007</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>7631</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>7283</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7191,97 +7191,97 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>4593</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>1605</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>2255</t>
-        </is>
-      </c>
-      <c r="U61" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>297601</t>
+          <t>298678</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>377165</t>
+          <t>377380</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>410338</t>
+          <t>409519</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>738779</t>
+          <t>751498</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>707691</t>
+          <t>711247</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1296498</t>
+          <t>1268306</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>582708</t>
+          <t>579787</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>668562</t>
+          <t>664475</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7662,12 +7662,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>144669</t>
+          <t>139712</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>330187</t>
+          <t>331517</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>674350</t>
+          <t>678979</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>976110</t>
+          <t>970829</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>287581</t>
+          <t>288537</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>362188</t>
+          <t>362358</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>72894</t>
+          <t>66658</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>169253</t>
+          <t>168381</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>350769</t>
+          <t>338533</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>509085</t>
+          <t>507459</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>91266</t>
+          <t>88624</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>147409</t>
+          <t>147119</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7888,12 +7888,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>109070</t>
+          <t>104431</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>179727</t>
+          <t>179532</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>78477</t>
+          <t>79998</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>12320</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>62473</t>
+          <t>61279</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>108772</t>
+          <t>110658</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8099,12 +8099,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>67878</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>48821</t>
+          <t>48095</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>88452</t>
+          <t>87868</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8297,12 +8297,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8375,12 +8375,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -8438,12 +8438,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8453,12 +8453,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8488,12 +8488,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>79666</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65701</t>
+          <t>65046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97421</t>
+          <t>96366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>70093</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55852</t>
+          <t>59686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77943</t>
+          <t>81277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>147525</t>
+          <t>149759</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>130358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168441</t>
+          <t>168078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>108481</t>
+          <t>114647</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>97759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126014</t>
+          <t>133034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62727</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>161070</t>
+          <t>173591</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144136</t>
+          <t>155319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>181565</t>
+          <t>194597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48233</t>
+          <t>60514</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36166</t>
+          <t>46729</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>77271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31585</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>25849</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41202</t>
+          <t>45669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>79818</t>
+          <t>95184</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>79196</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97353</t>
+          <t>115845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>27672</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40583</t>
+          <t>42308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>31486</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>46635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19833</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>14387</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,22 +1325,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10469</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6074</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>443673</t>
+          <t>476933</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443673</t>
+          <t>476933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>443673</t>
+          <t>476933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>49991</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35736</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61492</t>
+          <t>64004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57844</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>48004</t>
+          <t>51500</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67935</t>
+          <t>71100</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>106713</t>
+          <t>110640</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>94378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123700</t>
+          <t>126083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>98338</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78255</t>
+          <t>83571</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107781</t>
+          <t>112736</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43617</t>
+          <t>46602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>37432</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53049</t>
+          <t>55587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>137244</t>
+          <t>144940</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>120881</t>
+          <t>126641</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152572</t>
+          <t>162060</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>47008</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31385</t>
+          <t>35831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55802</t>
+          <t>60986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>57263</t>
+          <t>62959</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45507</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72025</t>
+          <t>78600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>22202</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10125</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10477</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20355</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>6701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>212172</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>212172</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212172</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>33618</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>45684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19369</t>
+          <t>21755</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>44415</t>
+          <t>49498</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>38316</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>85626</t>
+          <t>93671</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72503</t>
+          <t>78502</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101458</t>
+          <t>109623</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>97680</t>
+          <t>106830</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83651</t>
+          <t>92058</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112695</t>
+          <t>124371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>57057</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>43926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69565</t>
+          <t>73340</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10313</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>69163</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50490</t>
+          <t>54097</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>78607</t>
+          <t>85357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>18948</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12170</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>15743</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>846</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>736</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>868</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>806</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,57 +3942,57 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>4974</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>11901</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>11,25%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>4741</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>1567</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>10673</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>227069</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>227069</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>227069</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>99886</t>
+          <t>107981</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>80965</t>
+          <t>88290</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>122096</t>
+          <t>130723</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>288781</t>
+          <t>87722</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>155785</t>
+          <t>75007</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>374591</t>
+          <t>102900</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>388667</t>
+          <t>195703</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>227413</t>
+          <t>171691</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>648670</t>
+          <t>219440</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -4240,32 +4240,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>227840</t>
+          <t>245907</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>202311</t>
+          <t>222128</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>252090</t>
+          <t>270310</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4275,32 +4275,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>70981</t>
+          <t>77090</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>63158</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>150020</t>
+          <t>90185</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4310,32 +4310,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>298821</t>
+          <t>322997</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>144024</t>
+          <t>292862</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>394502</t>
+          <t>352549</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -4353,32 +4353,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>101427</t>
+          <t>110581</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>82373</t>
+          <t>92512</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>121926</t>
+          <t>131156</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>32981</t>
+          <t>36889</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>26854</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>72954</t>
+          <t>49320</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4423,32 +4423,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>134408</t>
+          <t>147471</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>124683</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>180817</t>
+          <t>173064</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>42116</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>26365</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>70486</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>11408</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>53525</t>
+          <t>51688</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>25626</t>
+          <t>37972</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>85754</t>
+          <t>68396</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>17839</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>27105</t>
+          <t>29075</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>34053</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12760</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>21504</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>33197</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4805,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>427</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5097</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -5144,17 +5144,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>46672</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>35187</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>64576</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5296,32 +5296,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>54666</t>
+          <t>63168</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>45545</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>74467</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5331,32 +5331,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>102059</t>
+          <t>109840</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>85733</t>
+          <t>93913</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>121251</t>
+          <t>129798</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -5374,32 +5374,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>93964</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>69297</t>
+          <t>78103</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>99349</t>
+          <t>111977</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5409,32 +5409,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>43568</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>52107</t>
+          <t>59279</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5444,32 +5444,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>127405</t>
+          <t>143758</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>109418</t>
+          <t>124372</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>144430</t>
+          <t>161697</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -5487,32 +5487,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>48674</t>
+          <t>55426</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>35870</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>62469</t>
+          <t>71981</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5522,32 +5522,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>25049</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>69077</t>
+          <t>80475</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>54933</t>
+          <t>65884</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>99037</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -5600,22 +5600,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>24452</t>
+          <t>26288</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5635,32 +5635,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>4998</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6235</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -5713,32 +5713,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>35699</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,32 +5748,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>26338</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>30720</t>
+          <t>40872</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22388</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5939,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>755</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5974,32 +5974,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1816</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>456</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6009,32 +6009,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10590</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10998</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6278,17 +6278,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6348,17 +6348,17 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -6395,32 +6395,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>48210</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6430,32 +6430,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>55943</t>
+          <t>55134</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>68455</t>
+          <t>66963</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6465,32 +6465,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>83010</t>
+          <t>76951</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>60278</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>105160</t>
+          <t>99243</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -6508,32 +6508,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>24212</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>12561</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>38932</t>
+          <t>36786</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6543,32 +6543,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>36939</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>44036</t>
+          <t>48015</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6578,32 +6578,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>57298</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>46125</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>77244</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -6621,32 +6621,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14336</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6656,32 +6656,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>11346</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>29723</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6691,32 +6691,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>45560</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>62782</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -6734,32 +6734,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>21632</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6769,32 +6769,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>449</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6804,32 +6804,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>10560</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>23387</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11547</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6882,32 +6882,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6917,32 +6917,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7030,32 +7030,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7977</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -7412,17 +7412,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7482,17 +7482,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>215138</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>215138</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>215138</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>333751</t>
+          <t>339745</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>298678</t>
+          <t>303833</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>377380</t>
+          <t>377977</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7564,32 +7564,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>538638</t>
+          <t>352646</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>409519</t>
+          <t>324395</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>751498</t>
+          <t>378117</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7599,32 +7599,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>872388</t>
+          <t>692391</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>711247</t>
+          <t>649259</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1268306</t>
+          <t>739896</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -7642,32 +7642,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>623623</t>
+          <t>669725</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>579787</t>
+          <t>625994</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>664475</t>
+          <t>712992</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7677,32 +7677,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>255895</t>
+          <t>282529</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>139712</t>
+          <t>258222</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>331517</t>
+          <t>307481</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>879518</t>
+          <t>952254</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>678979</t>
+          <t>906450</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>970829</t>
+          <t>1006146</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>40,09%</t>
         </is>
       </c>
     </row>
@@ -7755,32 +7755,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>323278</t>
+          <t>355659</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>288537</t>
+          <t>318482</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>362358</t>
+          <t>391524</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7790,32 +7790,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>127788</t>
+          <t>143758</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>66658</t>
+          <t>122837</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>168381</t>
+          <t>165322</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7825,32 +7825,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>451066</t>
+          <t>499416</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>338533</t>
+          <t>458205</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>507459</t>
+          <t>544453</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -7868,32 +7868,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>114555</t>
+          <t>112903</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>88624</t>
+          <t>89386</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>147119</t>
+          <t>136791</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7903,32 +7903,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>27354</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>25079</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>39268</t>
+          <t>47062</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7938,32 +7938,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>141909</t>
+          <t>147661</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>104431</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>179532</t>
+          <t>175370</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -7981,32 +7981,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>60191</t>
+          <t>72061</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>54515</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>79998</t>
+          <t>93698</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8016,32 +8016,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>40382</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8051,32 +8051,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>85413</t>
+          <t>100027</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>61279</t>
+          <t>79817</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>110658</t>
+          <t>125542</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -8094,32 +8094,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>49544</t>
+          <t>52592</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>35786</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>67878</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8129,32 +8129,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>21764</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>33552</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8164,32 +8164,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>66519</t>
+          <t>74356</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>87868</t>
+          <t>94429</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8207,27 +8207,27 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -8242,32 +8242,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>10115</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -8320,32 +8320,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8390,22 +8390,22 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -8433,32 +8433,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>30790</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8468,32 +8468,32 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8503,32 +8503,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>38008</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -8546,17 +8546,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1635731</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1635731</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1635731</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>1000502</t>
+          <t>873931</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>1000502</t>
+          <t>873931</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1000502</t>
+          <t>873931</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8616,17 +8616,17 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>2536219</t>
+          <t>2509662</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>2536219</t>
+          <t>2509662</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>2536219</t>
+          <t>2509662</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
